--- a/myapp/src/main/resources/plantilla3.xlsx
+++ b/myapp/src/main/resources/plantilla3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\App_TecnoMat\app_lectorArchivos\myapp\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B954DFA7-5F5B-4C3A-9C9F-51AA1AED263B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAFD7F8-9F7A-42B0-9782-6148F571CA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5130" yWindow="3165" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Listado" sheetId="1" r:id="rId1"/>
@@ -214,9 +214,6 @@
     <t>LISTADO MATERIALES ML</t>
   </si>
   <si>
-    <t>TS260001048</t>
-  </si>
-  <si>
     <t>La pica</t>
   </si>
   <si>
@@ -224,6 +221,9 @@
   </si>
   <si>
     <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>OT260001048</t>
   </si>
 </sst>
 </file>
@@ -992,7 +992,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="6"/>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="6"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="K5" s="45"/>
       <c r="L5" s="40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M5" s="41"/>
     </row>
@@ -1036,7 +1036,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" s="44"/>
       <c r="F6" s="6"/>

--- a/myapp/src/main/resources/plantilla3.xlsx
+++ b/myapp/src/main/resources/plantilla3.xlsx
@@ -2,50 +2,58 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\App_TecnoMat\app_lectorArchivos\myapp\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAFD7F8-9F7A-42B0-9782-6148F571CA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86FE09F-6299-4E0D-963F-C39B88DBA113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5130" yWindow="3165" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{501981FC-E882-4770-BB78-4C8F6F42D128}"/>
   </bookViews>
   <sheets>
-    <sheet name="Listado" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="68">
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Ref: Obra:</t>
+  </si>
+  <si>
+    <t>Cliente:</t>
+  </si>
+  <si>
+    <t>Respons:</t>
+  </si>
+  <si>
+    <t>Proyecto:</t>
+  </si>
+  <si>
+    <t>Impresión:</t>
+  </si>
+  <si>
+    <t>Entrega:</t>
+  </si>
+  <si>
     <t>A3</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Ref: Obra:</t>
-  </si>
-  <si>
-    <t>Cliente:</t>
-  </si>
-  <si>
-    <t>Respons:</t>
-  </si>
-  <si>
-    <t>Proyecto:</t>
-  </si>
-  <si>
-    <t>Impresión:</t>
-  </si>
-  <si>
-    <t>Entrega:</t>
-  </si>
-  <si>
     <t>MARCA</t>
   </si>
   <si>
@@ -211,19 +219,19 @@
     <t>Fijación s/perfilDPX³250 3P/4P</t>
   </si>
   <si>
-    <t>LISTADO MATERIALES ML</t>
-  </si>
-  <si>
-    <t>La pica</t>
-  </si>
-  <si>
-    <t>Ir a pescar</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>OT260001048</t>
+    <t>LISTADO MATERIALES CE</t>
+  </si>
+  <si>
+    <t>OT260001050</t>
+  </si>
+  <si>
+    <t>prueba4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pantalla </t>
+  </si>
+  <si>
+    <t>julio</t>
   </si>
 </sst>
 </file>
@@ -636,7 +644,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -648,8 +656,105 @@
 </styleSheet>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>7</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>180975</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>95250</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1026" name="Button 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1026"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="es-ES" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri"/>
+                  <a:cs typeface="Calibri"/>
+                </a:rPr>
+                <a:t>INSERTAR EN APP</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Hoja1"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="Hoja1.InsertarEnAtlas"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -659,44 +764,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -723,14 +828,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -757,6 +880,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -768,177 +909,157 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F1A8B88-0AFC-458C-BD32-B938E8DB4581}">
+  <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:M61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -953,7 +1074,7 @@
     </row>
     <row r="2" spans="1:13" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -970,7 +1091,7 @@
     </row>
     <row r="3" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="7"/>
@@ -985,14 +1106,14 @@
     </row>
     <row r="4" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="6"/>
@@ -1002,16 +1123,16 @@
       <c r="J4" s="13"/>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" spans="1:13" ht="36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="6"/>
@@ -1019,24 +1140,24 @@
       <c r="H5" s="26"/>
       <c r="I5" s="13"/>
       <c r="J5" s="45" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" s="45"/>
       <c r="L5" s="40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M5" s="41"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" s="44"/>
       <c r="F6" s="6"/>
@@ -1044,7 +1165,7 @@
       <c r="H6" s="27"/>
       <c r="I6" s="34"/>
       <c r="J6" s="46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K6" s="46"/>
       <c r="L6" s="42">
@@ -1063,7 +1184,7 @@
       <c r="H7" s="28"/>
       <c r="I7" s="34"/>
       <c r="J7" s="47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7" s="47"/>
       <c r="L7" s="42">
@@ -1073,7 +1194,7 @@
     </row>
     <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" s="33"/>
       <c r="C8" s="16"/>
@@ -1089,7 +1210,7 @@
     </row>
     <row r="9" spans="1:13" ht="24" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B9" s="31" t="s">
         <v>8</v>
@@ -1157,6 +1278,7 @@
       <c r="E12" s="21">
         <v>1</v>
       </c>
+      <c r="J12" s="38"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
@@ -1193,7 +1315,9 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="19"/>
+      <c r="A15" s="19">
+        <v>67768</v>
+      </c>
       <c r="B15" s="19" t="s">
         <v>21</v>
       </c>
@@ -1224,7 +1348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>79563</v>
       </c>
@@ -1241,7 +1365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>79564</v>
       </c>
@@ -1258,7 +1382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>71109</v>
       </c>
@@ -1275,7 +1399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>80696</v>
       </c>
@@ -1292,7 +1416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>80697</v>
       </c>
@@ -1308,9 +1432,8 @@
       <c r="E21" s="21">
         <v>1</v>
       </c>
-      <c r="I21" s="38"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>80698</v>
       </c>
@@ -1327,7 +1450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="19">
         <v>79672</v>
       </c>
@@ -1344,7 +1467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>80699</v>
       </c>
@@ -1361,7 +1484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="19">
         <v>80700</v>
       </c>
@@ -1378,7 +1501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>80701</v>
       </c>
@@ -1395,7 +1518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="19">
         <v>80702</v>
       </c>
@@ -1412,7 +1535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>79565</v>
       </c>
@@ -1429,7 +1552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="19">
         <v>79671</v>
       </c>
@@ -1446,7 +1569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>80703</v>
       </c>
@@ -1463,7 +1586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="19">
         <v>80704</v>
       </c>
@@ -1480,7 +1603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>79845</v>
       </c>
@@ -1838,7 +1961,9 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="19"/>
+      <c r="A53" s="19">
+        <v>90909</v>
+      </c>
       <c r="B53" s="19" t="s">
         <v>21</v>
       </c>
@@ -1999,6 +2124,37 @@
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="J7:K7"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1026" r:id="rId4" name="Button 2">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[1]!Hoja1.InsertarEnAtlas">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>7</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>14</xdr:row>
+                    <xdr:rowOff>180975</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>11</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>95250</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
 </worksheet>
 </file>